--- a/data/trans_dic/P1002-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,49</t>
+          <t>2,58; 5,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,49</t>
+          <t>4,79; 8,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,25</t>
+          <t>3,77; 7,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,8</t>
+          <t>3,7; 7,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,3; 17,87</t>
+          <t>12,36; 17,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,82; 13,91</t>
+          <t>9,15; 14,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,3</t>
+          <t>7,99; 11,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,61</t>
+          <t>3,49; 5,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,53</t>
+          <t>9,16; 12,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 10,29</t>
+          <t>7,23; 10,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,8</t>
+          <t>6,37; 8,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,86</t>
+          <t>4,03; 7,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,29</t>
+          <t>5,64; 9,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,22</t>
+          <t>2,91; 5,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,04</t>
+          <t>2,11; 6,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,11</t>
+          <t>5,65; 9,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,28; 16,71</t>
+          <t>12,48; 16,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 12,65</t>
+          <t>8,72; 12,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,94</t>
+          <t>8,74; 12,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,46</t>
+          <t>5,23; 7,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 12,37</t>
+          <t>9,51; 12,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,64</t>
+          <t>6,28; 8,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,25</t>
+          <t>4,92; 8,45</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,72</t>
+          <t>4,72; 8,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,94</t>
+          <t>4,01; 8,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,99</t>
+          <t>3,51; 6,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,1</t>
+          <t>5,77; 10,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 14,96</t>
+          <t>9,85; 14,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,76</t>
+          <t>10,5; 15,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 13,91</t>
+          <t>9,15; 13,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,56</t>
+          <t>3,7; 11,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,87; 10,98</t>
+          <t>7,81; 10,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,0</t>
+          <t>7,93; 11,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,67</t>
+          <t>6,8; 9,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 10,05</t>
+          <t>5,37; 9,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,06</t>
+          <t>3,93; 6,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,03</t>
+          <t>5,42; 8,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,46</t>
+          <t>5,32; 8,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,78</t>
+          <t>4,05; 6,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,09</t>
+          <t>7,64; 11,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,39; 15,71</t>
+          <t>11,52; 15,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,95</t>
+          <t>8,08; 12,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,33</t>
+          <t>9,06; 13,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 8,63</t>
+          <t>6,42; 8,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 11,78</t>
+          <t>9,1; 11,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,7</t>
+          <t>7,18; 9,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 9,88</t>
+          <t>7,3; 9,89</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,02</t>
+          <t>4,48; 6,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,75</t>
+          <t>5,85; 7,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,17</t>
+          <t>4,57; 6,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,32</t>
+          <t>4,17; 6,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 9,52</t>
+          <t>7,53; 9,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 15,19</t>
+          <t>12,89; 15,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 11,71</t>
+          <t>9,66; 11,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,08</t>
+          <t>8,03; 11,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,53</t>
+          <t>6,26; 7,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,17</t>
+          <t>9,69; 11,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,7</t>
+          <t>7,39; 8,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,55</t>
+          <t>6,75; 8,64</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17876; 38086</t>
+          <t>17929; 37659</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32729; 59711</t>
+          <t>33662; 61326</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29177; 54576</t>
+          <t>29118; 54588</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24415; 46051</t>
+          <t>23984; 46332</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25563; 46795</t>
+          <t>25449; 49060</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85731; 124592</t>
+          <t>86187; 125205</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59357; 93575</t>
+          <t>61582; 94769</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54190; 76277</t>
+          <t>53927; 76514</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49568; 77516</t>
+          <t>48286; 79264</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126906; 175547</t>
+          <t>128245; 177468</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97366; 138725</t>
+          <t>97478; 139215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>82861; 115381</t>
+          <t>83467; 114349</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36517; 65961</t>
+          <t>38760; 70377</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59682; 94437</t>
+          <t>57310; 92445</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29305; 53414</t>
+          <t>29777; 55173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26616; 72103</t>
+          <t>25195; 73114</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54466; 88200</t>
+          <t>54687; 87542</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>126718; 172464</t>
+          <t>128797; 174676</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91884; 131972</t>
+          <t>90899; 133817</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84043; 114358</t>
+          <t>83635; 116730</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>101520; 143977</t>
+          <t>100925; 145428</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>196397; 253460</t>
+          <t>194894; 255791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127623; 178472</t>
+          <t>129749; 180732</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>100731; 177459</t>
+          <t>105819; 181706</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31140; 59141</t>
+          <t>31994; 58207</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30318; 60151</t>
+          <t>30386; 60705</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26062; 53095</t>
+          <t>26684; 51946</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40013; 71172</t>
+          <t>40627; 72139</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67989; 102278</t>
+          <t>67371; 101554</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83359; 122349</t>
+          <t>81524; 123207</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72641; 109159</t>
+          <t>71828; 107637</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40984; 107936</t>
+          <t>34521; 108119</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>107150; 149605</t>
+          <t>106390; 149547</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121265; 168659</t>
+          <t>121629; 169538</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103983; 149291</t>
+          <t>104989; 149839</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90511; 164613</t>
+          <t>87957; 162801</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38099; 66538</t>
+          <t>37065; 63279</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50636; 85482</t>
+          <t>51280; 84327</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47997; 79279</t>
+          <t>49910; 82778</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36587; 62779</t>
+          <t>37490; 63348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76846; 115211</t>
+          <t>79400; 117032</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>119683; 165108</t>
+          <t>121093; 167083</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83289; 124750</t>
+          <t>84321; 125707</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100824; 145848</t>
+          <t>99191; 147566</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>123941; 170968</t>
+          <t>127124; 176632</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>178012; 235393</t>
+          <t>181705; 237271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>139989; 192220</t>
+          <t>142173; 191106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>145633; 199568</t>
+          <t>147385; 199820</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>146413; 197135</t>
+          <t>146756; 198797</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202429; 265576</t>
+          <t>200223; 262762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>157335; 209501</t>
+          <t>155036; 210026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>143983; 218652</t>
+          <t>144095; 218060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>253234; 321680</t>
+          <t>254321; 320284</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>458056; 540116</t>
+          <t>458486; 543955</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>341007; 415129</t>
+          <t>342362; 420308</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>297598; 405500</t>
+          <t>293952; 409591</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>416591; 501248</t>
+          <t>416760; 498152</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>674567; 780114</t>
+          <t>676277; 777108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>512014; 603749</t>
+          <t>512495; 607279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>477718; 608844</t>
+          <t>480796; 614848</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1002-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,43</t>
+          <t>2,71; 5,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,72</t>
+          <t>4,56; 8,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,09</t>
+          <t>4,37; 7,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,29</t>
+          <t>3,75; 7,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,13</t>
+          <t>3,7; 7,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 17,96</t>
+          <t>11,96; 17,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,08</t>
+          <t>9,04; 14,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,33</t>
+          <t>7,82; 11,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,73</t>
+          <t>3,57; 5,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 12,67</t>
+          <t>9,16; 12,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,33</t>
+          <t>7,24; 10,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,73</t>
+          <t>6,48; 8,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,32</t>
+          <t>3,97; 6,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,09</t>
+          <t>5,81; 9,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,4</t>
+          <t>2,79; 5,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,13</t>
+          <t>4,23; 6,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,04</t>
+          <t>5,66; 9,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,92</t>
+          <t>12,44; 16,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 12,83</t>
+          <t>8,62; 12,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 12,19</t>
+          <t>8,51; 11,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,53</t>
+          <t>5,18; 7,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 12,48</t>
+          <t>9,54; 12,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,75</t>
+          <t>6,18; 8,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,45</t>
+          <t>6,7; 8,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,58</t>
+          <t>4,59; 8,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,01</t>
+          <t>4,2; 7,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,84</t>
+          <t>3,34; 6,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 10,24</t>
+          <t>5,55; 9,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,85</t>
+          <t>9,95; 14,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 15,87</t>
+          <t>10,74; 15,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 13,71</t>
+          <t>9,19; 13,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,58</t>
+          <t>9,42; 13,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 10,98</t>
+          <t>7,86; 10,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,05</t>
+          <t>8,02; 11,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 9,7</t>
+          <t>6,73; 9,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 9,94</t>
+          <t>7,91; 10,98</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,72</t>
+          <t>4,0; 7,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,91</t>
+          <t>5,36; 8,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 8,83</t>
+          <t>5,19; 8,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,84</t>
+          <t>3,95; 6,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,27</t>
+          <t>7,65; 11,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,52; 15,9</t>
+          <t>11,53; 15,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 12,04</t>
+          <t>8,09; 11,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 13,48</t>
+          <t>10,16; 13,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 8,92</t>
+          <t>6,32; 8,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,1; 11,88</t>
+          <t>8,97; 11,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,65</t>
+          <t>7,17; 9,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 9,89</t>
+          <t>7,65; 9,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,07</t>
+          <t>4,53; 6,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,67</t>
+          <t>5,94; 7,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,19</t>
+          <t>4,66; 6,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,3</t>
+          <t>5,0; 6,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 9,48</t>
+          <t>7,59; 9,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,89; 15,3</t>
+          <t>12,89; 15,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,86</t>
+          <t>9,53; 11,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,19</t>
+          <t>9,98; 11,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,48</t>
+          <t>6,28; 7,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 11,13</t>
+          <t>9,71; 11,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,75</t>
+          <t>7,42; 8,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,64</t>
+          <t>7,72; 8,9</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>64137</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97653</t>
+          <t>107043</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17929; 37659</t>
+          <t>18779; 37908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33662; 61326</t>
+          <t>32087; 61610</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29118; 54588</t>
+          <t>29520; 53670</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23984; 46332</t>
+          <t>25930; 51118</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25449; 49060</t>
+          <t>25462; 48664</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86187; 125205</t>
+          <t>83357; 121814</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61582; 94769</t>
+          <t>60813; 94499</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53927; 76514</t>
+          <t>57264; 84182</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48286; 79264</t>
+          <t>49295; 79111</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>128245; 177468</t>
+          <t>128274; 174323</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97478; 139215</t>
+          <t>97547; 139991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83467; 114349</t>
+          <t>92156; 124726</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>57303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98373</t>
+          <t>109062</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>149514</t>
+          <t>166365</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38760; 70377</t>
+          <t>38231; 66145</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57310; 92445</t>
+          <t>59077; 93053</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29777; 55173</t>
+          <t>28523; 53118</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25195; 73114</t>
+          <t>44318; 72783</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54687; 87542</t>
+          <t>54789; 88434</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>128797; 174676</t>
+          <t>128448; 174874</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90899; 133817</t>
+          <t>89882; 131496</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83635; 116730</t>
+          <t>91022; 126897</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100925; 145428</t>
+          <t>99954; 142858</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>194894; 255791</t>
+          <t>195451; 252676</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129749; 180732</t>
+          <t>127571; 177980</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>105819; 181706</t>
+          <t>141938; 190347</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54414</t>
+          <t>58775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78934</t>
+          <t>90900</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>133348</t>
+          <t>149675</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31994; 58207</t>
+          <t>31121; 57750</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30386; 60705</t>
+          <t>31818; 60276</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26684; 51946</t>
+          <t>25398; 52380</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40627; 72139</t>
+          <t>44566; 77965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67371; 101554</t>
+          <t>68030; 101193</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81524; 123207</t>
+          <t>83369; 121346</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71828; 107637</t>
+          <t>72140; 109301</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34521; 108119</t>
+          <t>76545; 109074</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106390; 149547</t>
+          <t>107036; 149106</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121629; 169538</t>
+          <t>123041; 169654</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104989; 149839</t>
+          <t>104012; 148362</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87957; 162801</t>
+          <t>127741; 177371</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>123713</t>
+          <t>132536</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>172476</t>
+          <t>182692</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37065; 63279</t>
+          <t>37645; 66001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51280; 84327</t>
+          <t>50709; 84450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49910; 82778</t>
+          <t>48697; 82404</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37490; 63348</t>
+          <t>39050; 65091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79400; 117032</t>
+          <t>79470; 116484</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>121093; 167083</t>
+          <t>121206; 166821</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84321; 125707</t>
+          <t>84454; 125048</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>99191; 147566</t>
+          <t>113609; 151213</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>127124; 176632</t>
+          <t>125205; 172590</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181705; 237271</t>
+          <t>179190; 237212</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>142173; 191106</t>
+          <t>142016; 192467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>147385; 199820</t>
+          <t>161256; 205566</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187834</t>
+          <t>202972</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>365157</t>
+          <t>402803</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>552991</t>
+          <t>605775</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>146756; 198797</t>
+          <t>148464; 198912</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>200223; 262762</t>
+          <t>203429; 264601</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155036; 210026</t>
+          <t>158177; 210644</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144095; 218060</t>
+          <t>176467; 233558</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>254321; 320284</t>
+          <t>256407; 320052</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>458486; 543955</t>
+          <t>458375; 538013</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>342362; 420308</t>
+          <t>337941; 419802</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>293952; 409591</t>
+          <t>372575; 438334</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>416760; 498152</t>
+          <t>417963; 503940</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>676277; 777108</t>
+          <t>677517; 780673</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>512495; 607279</t>
+          <t>514784; 607076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>480796; 614848</t>
+          <t>560588; 646768</t>
         </is>
       </c>
     </row>
